--- a/TIC-TAC-TOE_Testcase 5.xlsx
+++ b/TIC-TAC-TOE_Testcase 5.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="94">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -376,9 +376,6 @@
 2. Observe the first player's turn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify </t>
-  </si>
-  <si>
     <t>1. Make a valid move.
 2. Observe the turn indicator.</t>
   </si>
@@ -413,6 +410,12 @@
     <t>1. Start a new game.
 2. Play multiple rounds using restart .
 3. Complete wins and draws.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhavana Mahalle</t>
+  </si>
+  <si>
+    <t>Verify that the game should correctly handle multiple rounds without errors, and each round should start with a clean board.</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -824,6 +827,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -972,24 +997,45 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1001,48 +1047,45 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1050,30 +1093,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1096,15 +1119,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>418347</xdr:colOff>
+      <xdr:colOff>289631</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>379713</xdr:rowOff>
+      <xdr:rowOff>426396</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
+      <xdr:colOff>437635</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>981524</xdr:rowOff>
+      <xdr:rowOff>1078062</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1121,8 +1144,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2690188" y="2979781"/>
-          <a:ext cx="1087633" cy="601811"/>
+          <a:off x="2561472" y="2865568"/>
+          <a:ext cx="1177734" cy="651666"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1141,11 +1164,11 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>193091</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>579301</xdr:rowOff>
+      <xdr:rowOff>628311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>611402</xdr:colOff>
+      <xdr:colOff>527736</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>1427534</xdr:rowOff>
     </xdr:to>
@@ -1164,8 +1187,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2464932" y="5309622"/>
-          <a:ext cx="1448041" cy="848233"/>
+          <a:off x="2464932" y="5358632"/>
+          <a:ext cx="1364375" cy="799223"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1435,10 +1458,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
+      <c r="B1" s="53"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1446,13 +1469,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="66"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="56"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1470,10 +1493,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="54"/>
+      <c r="B2" s="58"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1481,14 +1504,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="71" t="s">
+      <c r="G2" s="58"/>
+      <c r="H2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="54"/>
+      <c r="I2" s="58"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1509,10 +1532,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="54"/>
+      <c r="B3" s="58"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1520,14 +1543,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="72">
+      <c r="F3" s="61">
         <v>46220</v>
       </c>
-      <c r="G3" s="54"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="54"/>
+      <c r="I3" s="58"/>
       <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1578,21 +1601,21 @@
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="54"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="55"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="63"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1613,21 +1636,21 @@
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="54"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="5"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="55"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="63"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1648,21 +1671,21 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="54"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="5"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="55"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="63"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1683,17 +1706,17 @@
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="54"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="58"/>
       <c r="E8" s="5"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="52"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="55"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1714,17 +1737,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="57"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="67"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="56"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="68"/>
       <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1772,17 +1795,17 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1801,17 +1824,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1859,23 +1882,23 @@
       <c r="A14" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="63" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="64"/>
-      <c r="F14" s="63" t="s">
+      <c r="E14" s="53"/>
+      <c r="F14" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="63" t="s">
+      <c r="G14" s="55"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="66"/>
+      <c r="J14" s="56"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1896,23 +1919,23 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="52" t="s">
+      <c r="C15" s="58"/>
+      <c r="D15" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="52" t="s">
+      <c r="E15" s="58"/>
+      <c r="F15" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="52" t="s">
+      <c r="G15" s="62"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="55"/>
+      <c r="J15" s="63"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1933,23 +1956,23 @@
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="52" t="s">
+      <c r="C16" s="58"/>
+      <c r="D16" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="52" t="s">
+      <c r="E16" s="58"/>
+      <c r="F16" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="53"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="52" t="s">
+      <c r="G16" s="62"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="55"/>
+      <c r="J16" s="63"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1970,23 +1993,23 @@
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="52" t="s">
+      <c r="C17" s="58"/>
+      <c r="D17" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="54"/>
-      <c r="F17" s="52" t="s">
+      <c r="E17" s="58"/>
+      <c r="F17" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="53"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="52" t="s">
+      <c r="G17" s="62"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="55"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2007,23 +2030,23 @@
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="52" t="s">
+      <c r="C18" s="58"/>
+      <c r="D18" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="54"/>
-      <c r="F18" s="52" t="s">
+      <c r="E18" s="58"/>
+      <c r="F18" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="53"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="52" t="s">
+      <c r="G18" s="62"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="55"/>
+      <c r="J18" s="63"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2044,23 +2067,23 @@
       <c r="A19" s="25">
         <v>5</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="52" t="s">
+      <c r="C19" s="58"/>
+      <c r="D19" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="52" t="s">
+      <c r="E19" s="58"/>
+      <c r="F19" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="53"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="52" t="s">
+      <c r="G19" s="62"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="55"/>
+      <c r="J19" s="63"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2081,23 +2104,23 @@
       <c r="A20" s="25">
         <v>6</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="52" t="s">
+      <c r="C20" s="58"/>
+      <c r="D20" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="54"/>
-      <c r="F20" s="52" t="s">
+      <c r="E20" s="58"/>
+      <c r="F20" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="53"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="52" t="s">
+      <c r="G20" s="62"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="55"/>
+      <c r="J20" s="63"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2118,23 +2141,23 @@
       <c r="A21" s="25">
         <v>7</v>
       </c>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="54"/>
-      <c r="D21" s="52" t="s">
+      <c r="C21" s="58"/>
+      <c r="D21" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="54"/>
-      <c r="F21" s="52" t="s">
+      <c r="E21" s="58"/>
+      <c r="F21" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="53"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="52" t="s">
+      <c r="G21" s="62"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="55"/>
+      <c r="J21" s="63"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2155,23 +2178,23 @@
       <c r="A22" s="25">
         <v>8</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="52" t="s">
+      <c r="C22" s="58"/>
+      <c r="D22" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="54"/>
-      <c r="F22" s="52" t="s">
+      <c r="E22" s="58"/>
+      <c r="F22" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="53"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="52" t="s">
+      <c r="G22" s="62"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="55"/>
+      <c r="J22" s="63"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2192,15 +2215,15 @@
       <c r="A23" s="25">
         <v>9</v>
       </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="55"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="63"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2221,15 +2244,15 @@
       <c r="A24" s="25">
         <v>10</v>
       </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="55"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="63"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2250,15 +2273,15 @@
       <c r="A25" s="25">
         <v>11</v>
       </c>
-      <c r="B25" s="52"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="55"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="63"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2279,15 +2302,15 @@
       <c r="A26" s="25">
         <v>12</v>
       </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="55"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="63"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2308,15 +2331,15 @@
       <c r="A27" s="25">
         <v>13</v>
       </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="55"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="63"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2337,15 +2360,15 @@
       <c r="A28" s="25">
         <v>14</v>
       </c>
-      <c r="B28" s="52"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="55"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="63"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2366,15 +2389,15 @@
       <c r="A29" s="25">
         <v>15</v>
       </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="55"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="63"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2395,15 +2418,15 @@
       <c r="A30" s="25">
         <v>16</v>
       </c>
-      <c r="B30" s="52"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="55"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="63"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2424,15 +2447,15 @@
       <c r="A31" s="25">
         <v>17</v>
       </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="55"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="63"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2453,15 +2476,15 @@
       <c r="A32" s="25">
         <v>18</v>
       </c>
-      <c r="B32" s="52"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="55"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="63"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2482,15 +2505,15 @@
       <c r="A33" s="25">
         <v>19</v>
       </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="55"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="63"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2511,15 +2534,15 @@
       <c r="A34" s="26">
         <v>20</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="59"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="68"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28458,38 +28481,54 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="B25:C25"/>
@@ -28514,54 +28553,38 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1"/>
@@ -28588,10 +28611,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83"/>
+      <c r="B1" s="81"/>
       <c r="C1" s="27" t="s">
         <v>49</v>
       </c>
@@ -28599,19 +28622,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="29"/>
-      <c r="F1" s="92" t="s">
+      <c r="F1" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="85"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="84"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="79"/>
+      <c r="B2" s="76"/>
       <c r="C2" s="31" t="s">
         <v>51</v>
       </c>
@@ -28619,23 +28642,23 @@
         <v>6</v>
       </c>
       <c r="E2" s="33"/>
-      <c r="F2" s="78" t="s">
-        <v>48</v>
+      <c r="F2" s="79" t="s">
+        <v>92</v>
       </c>
-      <c r="G2" s="79"/>
-      <c r="H2" s="90" t="s">
+      <c r="G2" s="76"/>
+      <c r="H2" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="79"/>
+      <c r="I2" s="76"/>
       <c r="J2" s="34" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="79"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="31" t="s">
         <v>48</v>
       </c>
@@ -28643,14 +28666,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="33"/>
-      <c r="F3" s="94" t="s">
+      <c r="F3" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="79"/>
-      <c r="H3" s="90" t="s">
+      <c r="G3" s="76"/>
+      <c r="H3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="79"/>
+      <c r="I3" s="76"/>
       <c r="J3" s="35" t="s">
         <v>48</v>
       </c>
@@ -28671,93 +28694,93 @@
       <c r="A5" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="80"/>
-      <c r="D5" s="79"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="76"/>
       <c r="E5" s="40"/>
       <c r="F5" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="90" t="s">
+      <c r="G5" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="81"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="42">
         <v>1</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="80"/>
-      <c r="D6" s="79"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="76"/>
       <c r="E6" s="31"/>
       <c r="F6" s="43">
         <v>1</v>
       </c>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="81"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="42">
         <v>2</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="79"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="76"/>
       <c r="E7" s="31"/>
       <c r="F7" s="43">
         <v>2</v>
       </c>
-      <c r="G7" s="78" t="s">
+      <c r="G7" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="81"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="42">
         <v>3</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="79"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="76"/>
       <c r="E8" s="31"/>
       <c r="F8" s="43">
         <v>3</v>
       </c>
-      <c r="G8" s="78"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="81"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="44">
         <v>4</v>
       </c>
-      <c r="B9" s="74"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="75"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="90"/>
       <c r="E9" s="45"/>
       <c r="F9" s="46">
         <v>4</v>
       </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="77"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="91"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
@@ -28775,542 +28798,581 @@
       <c r="A11" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="87"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="50"/>
-      <c r="B12" s="88" t="s">
+      <c r="A12" s="49"/>
+      <c r="B12" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="87"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="87"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="82" t="s">
+      <c r="C14" s="81"/>
+      <c r="D14" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="83"/>
-      <c r="F14" s="82" t="s">
+      <c r="E14" s="81"/>
+      <c r="F14" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="82" t="s">
+      <c r="G14" s="83"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="85"/>
-    </row>
-    <row r="15" spans="1:10" ht="86.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="84"/>
+    </row>
+    <row r="15" spans="1:10" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42">
         <v>1</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="78" t="s">
+      <c r="C15" s="76"/>
+      <c r="D15" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="81"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="78"/>
     </row>
     <row r="16" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42">
         <v>2</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="78" t="s">
+      <c r="C16" s="76"/>
+      <c r="D16" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="79"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="81"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="78"/>
     </row>
     <row r="17" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="42">
         <v>3</v>
       </c>
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="78" t="s">
+      <c r="C17" s="76"/>
+      <c r="D17" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="79"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="81"/>
-    </row>
-    <row r="18" spans="1:10" ht="129" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="76"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="78"/>
+    </row>
+    <row r="18" spans="1:10" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42">
         <v>4</v>
       </c>
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="78" t="s">
+      <c r="C18" s="76"/>
+      <c r="D18" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="79"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="81"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="78"/>
     </row>
     <row r="19" spans="1:10" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42">
         <v>5</v>
       </c>
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="78" t="s">
+      <c r="C19" s="76"/>
+      <c r="D19" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="79"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="81"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="78"/>
     </row>
     <row r="20" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="42">
         <v>6</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="78" t="s">
+      <c r="C20" s="76"/>
+      <c r="D20" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="79"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="81"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42">
         <v>7</v>
       </c>
-      <c r="B21" s="78" t="s">
+      <c r="B21" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="78" t="s">
+      <c r="C21" s="76"/>
+      <c r="D21" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="79"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="81"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="22" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="42">
         <v>8</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="79"/>
-      <c r="D22" s="78" t="s">
+      <c r="C22" s="76"/>
+      <c r="D22" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="79"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="81"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="78"/>
     </row>
     <row r="23" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="42">
         <v>9</v>
       </c>
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="79"/>
-      <c r="D23" s="78" t="s">
+      <c r="C23" s="76"/>
+      <c r="D23" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="79"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="81"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="78"/>
     </row>
     <row r="24" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="42">
         <v>10</v>
       </c>
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="78" t="s">
+      <c r="C24" s="76"/>
+      <c r="D24" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="79"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="81"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="78"/>
     </row>
     <row r="25" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="42">
         <v>11</v>
       </c>
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="79"/>
-      <c r="D25" s="78" t="s">
+      <c r="C25" s="76"/>
+      <c r="D25" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="79"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="81"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="78"/>
     </row>
     <row r="26" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="42">
         <v>12</v>
       </c>
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="78" t="s">
+      <c r="C26" s="76"/>
+      <c r="D26" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="E26" s="79"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="81"/>
+      <c r="E26" s="76"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="78"/>
     </row>
     <row r="27" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="42">
         <v>13</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="79"/>
-      <c r="D27" s="78" t="s">
+      <c r="C27" s="76"/>
+      <c r="D27" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="79"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="81"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="78"/>
     </row>
     <row r="28" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="42">
         <v>14</v>
       </c>
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="78" t="s">
+      <c r="C28" s="76"/>
+      <c r="D28" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="E28" s="79"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="81"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="78"/>
     </row>
     <row r="29" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="42">
         <v>15</v>
       </c>
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="79"/>
-      <c r="D29" s="78" t="s">
-        <v>86</v>
+      <c r="C29" s="76"/>
+      <c r="D29" s="79" t="s">
+        <v>85</v>
       </c>
-      <c r="E29" s="79"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="81"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="78"/>
     </row>
     <row r="30" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="42">
         <v>16</v>
       </c>
-      <c r="B30" s="78" t="s">
+      <c r="B30" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="76"/>
+      <c r="D30" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="79"/>
-      <c r="D30" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="81"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="78"/>
     </row>
     <row r="31" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="42">
         <v>17</v>
       </c>
-      <c r="B31" s="78" t="s">
-        <v>85</v>
+      <c r="B31" s="79" t="s">
+        <v>84</v>
       </c>
-      <c r="C31" s="79"/>
-      <c r="D31" s="78" t="s">
-        <v>87</v>
+      <c r="C31" s="76"/>
+      <c r="D31" s="79" t="s">
+        <v>86</v>
       </c>
-      <c r="E31" s="79"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="81"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="78"/>
     </row>
     <row r="32" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="42">
         <v>18</v>
       </c>
-      <c r="B32" s="78" t="s">
+      <c r="B32" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="76"/>
+      <c r="D32" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="79"/>
-      <c r="D32" s="78" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="79"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="81"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="78"/>
     </row>
     <row r="33" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="42">
         <v>19</v>
       </c>
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="76"/>
+      <c r="D33" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="79"/>
-      <c r="D33" s="78" t="s">
-        <v>91</v>
-      </c>
-      <c r="E33" s="79"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="81"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="78"/>
     </row>
     <row r="34" spans="1:10" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="42">
         <v>20</v>
       </c>
-      <c r="B34" s="74" t="s">
-        <v>92</v>
+      <c r="B34" s="88" t="s">
+        <v>91</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="95" t="s">
-        <v>82</v>
+      <c r="C34" s="89"/>
+      <c r="D34" s="79" t="s">
+        <v>93</v>
       </c>
-      <c r="E34" s="96"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="77"/>
-    </row>
-    <row r="35" spans="1:10" s="49" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="74"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="77"/>
-    </row>
+      <c r="E34" s="75"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="88"/>
+      <c r="J34" s="91"/>
+    </row>
+    <row r="35" spans="1:10" s="51" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="50"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="50"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="50"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="50"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="50"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="50"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="106">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G7:J7"/>
+  <mergeCells count="103">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="A2:B2"/>
@@ -29323,10 +29385,6 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="B9:D9"/>
@@ -29349,64 +29407,16 @@
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
